--- a/data/trans_orig/P44A$endoscopia-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P44A$endoscopia-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de prueba realizada para detectar cáncer de colon-recto (multirrespuesta) en 2012</t>
+          <t>Población según el tipo de prueba realizada para detectar cáncer de colon-recto (multirrespuesta) en 2012 (tasa de respuesta: 96,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20884</t>
+          <t>21267</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34410</t>
+          <t>34683</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34295</t>
+          <t>33304</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49422</t>
+          <t>48307</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59711</t>
+          <t>59781</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80076</t>
+          <t>79589</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>73,72%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13136</t>
+          <t>13522</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2185</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11697</t>
+          <t>12597</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7249</t>
+          <t>7880</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20698</t>
+          <t>21193</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,63%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12223</t>
+          <t>12005</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25637</t>
+          <t>25955</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11416</t>
+          <t>11517</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26220</t>
+          <t>26355</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27445</t>
+          <t>28055</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>48677</t>
+          <t>47700</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>44,18%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11088</t>
+          <t>11136</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>14233</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28332</t>
+          <t>29187</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17621</t>
+          <t>17735</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37074</t>
+          <t>36034</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>33,37%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21803</t>
+          <t>21669</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36680</t>
+          <t>36841</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10580</t>
+          <t>10427</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21996</t>
+          <t>22490</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>35844</t>
+          <t>36925</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>54639</t>
+          <t>55203</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,84%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>4143</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17338</t>
+          <t>16429</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5995</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5265</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>19310</t>
+          <t>19572</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,41%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9973</t>
+          <t>10853</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24447</t>
+          <t>24678</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5038</t>
+          <t>5812</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17000</t>
+          <t>16764</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19865</t>
+          <t>19284</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38067</t>
+          <t>37168</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>46,35%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7091</t>
+          <t>7288</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21298</t>
+          <t>21238</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6897</t>
+          <t>6682</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17776</t>
+          <t>18188</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16377</t>
+          <t>16261</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33877</t>
+          <t>33379</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>41,63%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4599</t>
+          <t>4528</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12711</t>
+          <t>12722</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2862</t>
+          <t>2867</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10069</t>
+          <t>10119</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10124</t>
+          <t>9569</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>21042</t>
+          <t>20955</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,46%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>880</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7718</t>
+          <t>7666</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>4288</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9377</t>
+          <t>9265</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,25%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9866</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>1221</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8471</t>
+          <t>8445</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4939</t>
+          <t>5098</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15260</t>
+          <t>15639</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>57,81%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1204</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9158</t>
+          <t>9123</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>10547</t>
+          <t>10384</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,39%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56432</t>
+          <t>57249</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>78039</t>
+          <t>77847</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>54870</t>
+          <t>54574</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>76486</t>
+          <t>74671</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>116498</t>
+          <t>116173</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>148014</t>
+          <t>146191</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>67,93%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12122</t>
+          <t>12226</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30912</t>
+          <t>29752</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4345</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16588</t>
+          <t>16239</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19516</t>
+          <t>19563</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40442</t>
+          <t>41357</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,22%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30607</t>
+          <t>30546</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>52072</t>
+          <t>53643</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24522</t>
+          <t>24608</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45100</t>
+          <t>44330</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>60376</t>
+          <t>59401</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>90172</t>
+          <t>90640</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>42,12%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10251</t>
+          <t>10773</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27241</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27539</t>
+          <t>28655</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>47713</t>
+          <t>48710</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>42340</t>
+          <t>42415</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>69253</t>
+          <t>69319</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,21%</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de prueba realizada para detectar cáncer de colon-recto (multirrespuesta) en 2016</t>
+          <t>Población según el tipo de prueba realizada para detectar cáncer de colon-recto (multirrespuesta) en 2016 (tasa de respuesta: 96,56%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23236</t>
+          <t>23722</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36818</t>
+          <t>37308</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26177</t>
+          <t>25526</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42861</t>
+          <t>41849</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53899</t>
+          <t>53489</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>76094</t>
+          <t>74026</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>65,03%</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1744</t>
+          <t>1770</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9254</t>
+          <t>9344</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3113</t>
+          <t>3295</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14210</t>
+          <t>14339</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6668</t>
+          <t>6472</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20226</t>
+          <t>19840</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,43%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10350</t>
+          <t>10737</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23436</t>
+          <t>23679</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16653</t>
+          <t>17240</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32890</t>
+          <t>33879</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>31276</t>
+          <t>30547</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>51936</t>
+          <t>52049</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,73%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>6545</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18153</t>
+          <t>18550</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5424</t>
+          <t>5690</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18832</t>
+          <t>19277</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15479</t>
+          <t>15427</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33078</t>
+          <t>32324</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,4%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>31632</t>
+          <t>30927</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49445</t>
+          <t>48902</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13081</t>
+          <t>13659</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26612</t>
+          <t>25980</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>49389</t>
+          <t>49866</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>71310</t>
+          <t>71171</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>62,15%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14659</t>
+          <t>14680</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5229</t>
+          <t>5239</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>3601</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>16358</t>
+          <t>15328</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21475</t>
+          <t>21004</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38887</t>
+          <t>38715</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5186</t>
+          <t>5426</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16344</t>
+          <t>17302</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29645</t>
+          <t>30613</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50748</t>
+          <t>50991</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,52%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7908</t>
+          <t>7563</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22260</t>
+          <t>22577</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7404</t>
+          <t>7290</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19132</t>
+          <t>19182</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18282</t>
+          <t>18272</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36949</t>
+          <t>36446</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>31,82%</t>
         </is>
       </c>
     </row>
@@ -3699,12 +3699,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17725</t>
+          <t>18398</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4122</t>
+          <t>4155</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12988</t>
+          <t>12990</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14174</t>
+          <t>13579</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28744</t>
+          <t>28646</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,54%</t>
         </is>
       </c>
     </row>
@@ -3812,12 +3812,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10875</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5489</t>
+          <t>5116</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2440</t>
+          <t>2709</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11641</t>
+          <t>12058</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,74%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6901</t>
+          <t>6986</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18092</t>
+          <t>17183</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9707</t>
+          <t>9950</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10065</t>
+          <t>9540</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24097</t>
+          <t>23533</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>52,19%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>5262</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17083</t>
+          <t>16750</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2287</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11686</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>9927</t>
+          <t>9622</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>23753</t>
+          <t>25074</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>55,61%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>69110</t>
+          <t>69564</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>94943</t>
+          <t>96353</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52211</t>
+          <t>51702</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>75076</t>
+          <t>74095</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>129631</t>
+          <t>128610</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>162995</t>
+          <t>162161</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>59,3%</t>
         </is>
       </c>
     </row>
@@ -4268,12 +4268,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10104</t>
+          <t>9967</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26414</t>
+          <t>26801</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4916</t>
+          <t>4977</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17786</t>
+          <t>16132</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18172</t>
+          <t>17704</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>38491</t>
+          <t>38096</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>46678</t>
+          <t>46210</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>70850</t>
+          <t>70195</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>29791</t>
+          <t>28283</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>51638</t>
+          <t>51299</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>82881</t>
+          <t>81280</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>116076</t>
+          <t>112386</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>41,1%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26132</t>
+          <t>25249</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>46946</t>
+          <t>48401</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21362</t>
+          <t>20627</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41128</t>
+          <t>41624</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>52767</t>
+          <t>51476</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>83010</t>
+          <t>81324</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>29,74%</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de prueba realizada para detectar cáncer de colon-recto (multirrespuesta) en 2023</t>
+          <t>Población según el tipo de prueba realizada para detectar cáncer de colon-recto (multirrespuesta) en 2023 (tasa de respuesta: 99,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51522</t>
+          <t>51904</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70427</t>
+          <t>71864</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>61354</t>
+          <t>62406</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>80219</t>
+          <t>80651</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>118644</t>
+          <t>120248</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>144300</t>
+          <t>147208</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>47,43%</t>
         </is>
       </c>
     </row>
@@ -4955,12 +4955,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79717</t>
+          <t>79658</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>98464</t>
+          <t>98723</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>106830</t>
+          <t>107554</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>123933</t>
+          <t>124709</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>192414</t>
+          <t>191855</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>218077</t>
+          <t>217802</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>70,17%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8714</t>
+          <t>9465</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21744</t>
+          <t>21669</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15340</t>
+          <t>15888</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28847</t>
+          <t>28982</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28619</t>
+          <t>28227</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>45487</t>
+          <t>46570</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>3780</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3270</t>
+          <t>3407</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>579</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5632</t>
+          <t>5659</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>190390</t>
+          <t>188560</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>463179</t>
+          <t>461292</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>66011</t>
+          <t>66265</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>86904</t>
+          <t>86645</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>257878</t>
+          <t>259063</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>604516</t>
+          <t>606503</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,67%</t>
         </is>
       </c>
     </row>
@@ -5411,12 +5411,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>339094</t>
+          <t>337393</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>484205</t>
+          <t>486645</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>148722</t>
+          <t>150358</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>169036</t>
+          <t>169173</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>502878</t>
+          <t>504675</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>672095</t>
+          <t>674347</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,92%</t>
         </is>
       </c>
     </row>
@@ -5524,12 +5524,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>74940</t>
+          <t>75625</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>445512</t>
+          <t>445404</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20239</t>
+          <t>19780</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34678</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>96733</t>
+          <t>97790</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>559915</t>
+          <t>558372</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,11%</t>
         </is>
       </c>
     </row>
@@ -5642,7 +5642,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>7141</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>4563</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5707,12 +5707,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>623</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>51237</t>
+          <t>51526</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>70671</t>
+          <t>71490</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22037</t>
+          <t>21493</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>33831</t>
+          <t>34228</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>76420</t>
+          <t>76539</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>100977</t>
+          <t>100429</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,07%</t>
         </is>
       </c>
     </row>
@@ -5867,12 +5867,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63742</t>
+          <t>64124</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83807</t>
+          <t>83815</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55785</t>
+          <t>56406</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67638</t>
+          <t>67989</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>124931</t>
+          <t>125030</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>148245</t>
+          <t>148772</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>71,21%</t>
         </is>
       </c>
     </row>
@@ -5980,12 +5980,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8388</t>
+          <t>7740</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21284</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2833</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9835</t>
+          <t>9215</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12003</t>
+          <t>12630</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>26903</t>
+          <t>27237</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,04%</t>
         </is>
       </c>
     </row>
@@ -6093,97 +6093,97 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>1484</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>1028</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>1261</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>321402</t>
+          <t>320734</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>644058</t>
+          <t>644745</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>158068</t>
+          <t>159143</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>188697</t>
+          <t>189444</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>485247</t>
+          <t>486587</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>914955</t>
+          <t>933104</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>74,47%</t>
         </is>
       </c>
     </row>
@@ -6323,12 +6323,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>492476</t>
+          <t>494371</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>694884</t>
+          <t>695326</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6358,12 +6358,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>323638</t>
+          <t>323663</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>353144</t>
+          <t>351987</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6393,12 +6393,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>837950</t>
+          <t>839521</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1087480</t>
+          <t>1088090</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,84%</t>
         </is>
       </c>
     </row>
@@ -6436,12 +6436,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>97996</t>
+          <t>96392</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>580197</t>
+          <t>575108</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6451,12 +6451,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44190</t>
+          <t>44454</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>64092</t>
+          <t>64367</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6486,12 +6486,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>148249</t>
+          <t>149400</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>746725</t>
+          <t>791177</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>63,15%</t>
         </is>
       </c>
     </row>
@@ -6549,12 +6549,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>488</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8074</t>
+          <t>8392</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6564,12 +6564,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>594</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5927</t>
+          <t>5537</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6599,12 +6599,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1819</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10556</t>
+          <t>10570</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">

--- a/data/trans_orig/P44A$endoscopia-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P44A$endoscopia-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21267</t>
+          <t>20547</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34683</t>
+          <t>34084</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33304</t>
+          <t>34445</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48307</t>
+          <t>49547</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59781</t>
+          <t>58939</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79589</t>
+          <t>80166</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>74,25%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3074</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13522</t>
+          <t>13156</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2803</t>
+          <t>2950</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12597</t>
+          <t>12699</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7880</t>
+          <t>7268</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21193</t>
+          <t>21138</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,58%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12005</t>
+          <t>12360</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25955</t>
+          <t>26843</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11517</t>
+          <t>11397</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26355</t>
+          <t>26446</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28055</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>47700</t>
+          <t>48360</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>44,79%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11136</t>
+          <t>10921</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14233</t>
+          <t>13608</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29187</t>
+          <t>29013</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17735</t>
+          <t>17297</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36034</t>
+          <t>35677</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,04%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21669</t>
+          <t>22074</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36841</t>
+          <t>36666</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10427</t>
+          <t>9369</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22490</t>
+          <t>21886</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>36925</t>
+          <t>36246</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>55203</t>
+          <t>54932</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>68,5%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4143</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16429</t>
+          <t>16811</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>7283</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>6321</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>19572</t>
+          <t>20500</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>25,56%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10853</t>
+          <t>10078</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24678</t>
+          <t>25083</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5812</t>
+          <t>5112</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16764</t>
+          <t>16856</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19284</t>
+          <t>18322</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37168</t>
+          <t>37287</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,5%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7288</t>
+          <t>7132</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21238</t>
+          <t>20732</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6682</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18188</t>
+          <t>18310</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16261</t>
+          <t>16106</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33379</t>
+          <t>34141</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>42,58%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>5293</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12722</t>
+          <t>12673</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2867</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10119</t>
+          <t>9956</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9569</t>
+          <t>9472</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20955</t>
+          <t>20870</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,15%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>932</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7666</t>
+          <t>7726</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>4352</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>968</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9265</t>
+          <t>8755</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>32,36%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>9705</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8445</t>
+          <t>8383</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5098</t>
+          <t>5171</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15639</t>
+          <t>16163</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>59,75%</t>
         </is>
       </c>
     </row>
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2067</t>
+          <t>1698</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9123</t>
+          <t>9238</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>10384</t>
+          <t>11945</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>44,16%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57249</t>
+          <t>55486</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>77847</t>
+          <t>78290</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>54574</t>
+          <t>53655</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74671</t>
+          <t>75099</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>116173</t>
+          <t>115078</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>146191</t>
+          <t>145219</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>67,48%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12226</t>
+          <t>12508</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29752</t>
+          <t>30662</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4124</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16239</t>
+          <t>16285</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19563</t>
+          <t>20032</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41357</t>
+          <t>40898</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,0%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30546</t>
+          <t>31229</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>53643</t>
+          <t>52413</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24608</t>
+          <t>24662</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44330</t>
+          <t>43058</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>59401</t>
+          <t>61098</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>90640</t>
+          <t>88984</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>41,35%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10773</t>
+          <t>10363</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>27833</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28655</t>
+          <t>27408</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48710</t>
+          <t>48542</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>42415</t>
+          <t>42697</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>69319</t>
+          <t>69718</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,4%</t>
         </is>
       </c>
     </row>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23722</t>
+          <t>23379</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37308</t>
+          <t>36357</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25526</t>
+          <t>26676</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41849</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53489</t>
+          <t>54344</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74026</t>
+          <t>76022</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>66,79%</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>1738</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9344</t>
+          <t>9134</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3295</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14339</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6472</t>
+          <t>7032</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19840</t>
+          <t>21082</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10737</t>
+          <t>11120</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23679</t>
+          <t>23541</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17240</t>
+          <t>16676</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>33879</t>
+          <t>33461</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>30547</t>
+          <t>30619</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>52049</t>
+          <t>51445</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,19%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6545</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18550</t>
+          <t>17979</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5690</t>
+          <t>6169</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19277</t>
+          <t>18950</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15427</t>
+          <t>14616</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32324</t>
+          <t>32207</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,29%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>30927</t>
+          <t>31025</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>48902</t>
+          <t>48656</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13659</t>
+          <t>13892</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25980</t>
+          <t>25827</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>49866</t>
+          <t>48897</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>71171</t>
+          <t>71280</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,24%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3087</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14680</t>
+          <t>14701</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5239</t>
+          <t>5430</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3601</t>
+          <t>4029</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>15328</t>
+          <t>18166</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>15,86%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21004</t>
+          <t>21385</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38715</t>
+          <t>39459</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5426</t>
+          <t>5450</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17302</t>
+          <t>16359</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30613</t>
+          <t>29598</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50991</t>
+          <t>49652</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>43,36%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7563</t>
+          <t>7909</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22577</t>
+          <t>21566</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7290</t>
+          <t>7261</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19182</t>
+          <t>18768</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18272</t>
+          <t>18654</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36446</t>
+          <t>37065</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>32,36%</t>
         </is>
       </c>
     </row>
@@ -3699,12 +3699,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>7199</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18398</t>
+          <t>17996</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4155</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12990</t>
+          <t>13114</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13579</t>
+          <t>14163</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28646</t>
+          <t>28356</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>62,89%</t>
         </is>
       </c>
     </row>
@@ -3812,12 +3812,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1875</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10875</t>
+          <t>10281</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5116</t>
+          <t>5625</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>2728</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12058</t>
+          <t>11209</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>24,86%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6986</t>
+          <t>6330</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17183</t>
+          <t>17284</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>1871</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9950</t>
+          <t>10140</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9540</t>
+          <t>10752</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23533</t>
+          <t>24810</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>55,03%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5262</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16750</t>
+          <t>16693</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11686</t>
+          <t>11226</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>9622</t>
+          <t>9019</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>25074</t>
+          <t>24018</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>53,27%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>69564</t>
+          <t>70560</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96353</t>
+          <t>94667</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51702</t>
+          <t>51968</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74095</t>
+          <t>74129</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>128610</t>
+          <t>128072</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>162161</t>
+          <t>162920</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>59,58%</t>
         </is>
       </c>
     </row>
@@ -4268,12 +4268,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9967</t>
+          <t>10323</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26801</t>
+          <t>26755</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4977</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16132</t>
+          <t>17336</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17704</t>
+          <t>17549</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>38096</t>
+          <t>37839</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>46210</t>
+          <t>46065</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>70195</t>
+          <t>69951</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28283</t>
+          <t>27746</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>51299</t>
+          <t>50767</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>81280</t>
+          <t>82579</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>112386</t>
+          <t>115764</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>42,34%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25249</t>
+          <t>25029</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>48401</t>
+          <t>46479</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20627</t>
+          <t>21145</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41624</t>
+          <t>41306</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>51476</t>
+          <t>51560</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>81324</t>
+          <t>80934</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,6%</t>
         </is>
       </c>
     </row>
@@ -4837,32 +4837,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>61706</t>
+          <t>66204</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51904</t>
+          <t>54941</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71864</t>
+          <t>77295</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4872,32 +4872,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>70681</t>
+          <t>77206</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>62406</t>
+          <t>67795</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>80651</t>
+          <t>87525</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4907,32 +4907,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>132387</t>
+          <t>143410</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>120248</t>
+          <t>130154</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>147208</t>
+          <t>157602</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>46,86%</t>
         </is>
       </c>
     </row>
@@ -4950,32 +4950,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>89333</t>
+          <t>95144</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79658</t>
+          <t>85065</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>98723</t>
+          <t>104877</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4985,32 +4985,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>115858</t>
+          <t>127217</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>107554</t>
+          <t>117632</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>124709</t>
+          <t>136118</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5020,17 +5020,17 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>205191</t>
+          <t>222360</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>191855</t>
+          <t>209048</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>217802</t>
+          <t>235651</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>70,06%</t>
         </is>
       </c>
     </row>
@@ -5063,32 +5063,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14594</t>
+          <t>15917</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9465</t>
+          <t>10396</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21669</t>
+          <t>24111</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5098,32 +5098,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>21820</t>
+          <t>24697</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15888</t>
+          <t>17774</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28982</t>
+          <t>32853</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5133,32 +5133,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>36414</t>
+          <t>40614</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28227</t>
+          <t>31597</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>46570</t>
+          <t>50946</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -5176,7 +5176,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1204</t>
+          <t>1182</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -5186,12 +5186,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>3577</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>4287</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5246,32 +5246,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2168</t>
+          <t>2217</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>574</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5659</t>
+          <t>5348</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -5293,32 +5293,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>346926</t>
+          <t>115134</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>188560</t>
+          <t>99982</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>461292</t>
+          <t>130146</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5328,32 +5328,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>76003</t>
+          <t>84825</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>66265</t>
+          <t>73744</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>86645</t>
+          <t>96250</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5363,32 +5363,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>422928</t>
+          <t>199959</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>259063</t>
+          <t>181551</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>606503</t>
+          <t>219867</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>41,13%</t>
         </is>
       </c>
     </row>
@@ -5406,32 +5406,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>425270</t>
+          <t>194244</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>337393</t>
+          <t>179140</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>486645</t>
+          <t>208775</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5441,32 +5441,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>159813</t>
+          <t>174602</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>150358</t>
+          <t>163745</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>169173</t>
+          <t>185699</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5476,32 +5476,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>585083</t>
+          <t>368845</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>504675</t>
+          <t>348359</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>674347</t>
+          <t>386363</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>72,27%</t>
         </is>
       </c>
     </row>
@@ -5519,32 +5519,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>287159</t>
+          <t>45377</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>75625</t>
+          <t>34024</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>445404</t>
+          <t>57496</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5554,32 +5554,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>26700</t>
+          <t>30327</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19780</t>
+          <t>21781</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>39392</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5589,32 +5589,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>313859</t>
+          <t>75704</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>97790</t>
+          <t>61464</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>558372</t>
+          <t>90371</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>16,9%</t>
         </is>
       </c>
     </row>
@@ -5632,67 +5632,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2165</t>
+          <t>2293</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>514</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6950</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>7141</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>4040</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>1166</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>4563</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5702,32 +5702,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>3330</t>
+          <t>3448</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>8696</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -5749,32 +5749,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>60588</t>
+          <t>64869</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>51526</t>
+          <t>54247</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>71490</t>
+          <t>75141</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5784,32 +5784,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>27620</t>
+          <t>30154</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21493</t>
+          <t>23845</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>34228</t>
+          <t>37032</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5819,32 +5819,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>88208</t>
+          <t>95023</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>76539</t>
+          <t>83687</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>100429</t>
+          <t>107798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>47,67%</t>
         </is>
       </c>
     </row>
@@ -5862,32 +5862,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>74442</t>
+          <t>76854</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64124</t>
+          <t>65755</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83815</t>
+          <t>86562</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5897,32 +5897,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>62335</t>
+          <t>71085</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56406</t>
+          <t>63996</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67989</t>
+          <t>77189</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5932,32 +5932,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>136777</t>
+          <t>147939</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>125030</t>
+          <t>135767</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>148772</t>
+          <t>160560</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,0%</t>
         </is>
       </c>
     </row>
@@ -5975,102 +5975,102 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>13514</t>
+          <t>13986</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7740</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>21479</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>6,14%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>16,58%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>7053</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>3648</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>11550</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>7,3%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>3,78%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>11,96%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>21040</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>14151</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>29215</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>9,3%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>6,26%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>17,0%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>5403</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>2644</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>9215</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>6,34%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>3,1%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>10,82%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>18917</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>12630</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>27237</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>9,05%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>6,05%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -6205,32 +6205,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>469220</t>
+          <t>246207</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>320734</t>
+          <t>224605</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>644745</t>
+          <t>266587</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6240,32 +6240,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>174304</t>
+          <t>192185</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>159143</t>
+          <t>176466</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>189444</t>
+          <t>209550</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6275,32 +6275,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>643524</t>
+          <t>438392</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>486587</t>
+          <t>410363</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>933104</t>
+          <t>465037</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>42,39%</t>
         </is>
       </c>
     </row>
@@ -6318,32 +6318,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>589045</t>
+          <t>366242</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>494371</t>
+          <t>345589</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>695326</t>
+          <t>387707</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6353,32 +6353,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>338007</t>
+          <t>372902</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>323663</t>
+          <t>356019</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>351987</t>
+          <t>388187</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6388,32 +6388,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>927052</t>
+          <t>739145</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>839521</t>
+          <t>714309</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1088090</t>
+          <t>766440</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>69,86%</t>
         </is>
       </c>
     </row>
@@ -6431,32 +6431,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>315266</t>
+          <t>75280</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>96392</t>
+          <t>60347</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>575108</t>
+          <t>91760</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6466,32 +6466,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>53924</t>
+          <t>62077</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44454</t>
+          <t>51114</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>64367</t>
+          <t>73872</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6501,32 +6501,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>369190</t>
+          <t>137357</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>149400</t>
+          <t>120305</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>791177</t>
+          <t>157802</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -6544,69 +6544,69 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>3475</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8392</t>
+          <t>8071</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>2190</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5722</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
           <t>1,08%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>2131</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>594</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5537</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>9</t>
@@ -6614,32 +6614,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>5499</t>
+          <t>5665</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1819</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10570</t>
+          <t>10540</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
